--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:15</t>
+    <t xml:space="preserve">2026-09-09 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:59</t>
+    <t xml:space="preserve">2026-09-17 13:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:47</t>
+    <t xml:space="preserve">2026-10-05 18:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -578,7 +578,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>956815.12</v>
+        <v>956815.13</v>
       </c>
     </row>
     <row r="14">
@@ -610,7 +610,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>674451.62</v>
+        <v>674451.63</v>
       </c>
     </row>
   </sheetData>
